--- a/daily_matches/job_matches_2026-03-04.xlsx
+++ b/daily_matches/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,200 +468,200 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer/Python Developer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, S3, EC2, Data Lake, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, XGBoost, AWS SageMaker</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, MLflow, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=77ec677a15d6a6e0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Senior Applied Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Synapse, MLflow, Docker, CI/CD, Git, Snowflake, Power BI, Python</t>
+          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa864f5aa69daed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>Senior Applied Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, BigQuery, CI/CD, Terraform, Snowflake, BigQuery, PySpark, Kafka</t>
+          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=118577285ec0c152</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Systems Engineer (Agentic &amp; Automation)</t>
+          <t>Senior Applied Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a255a4464a88677</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8163b8efebf920</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Scientist II - Reservations</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb19b5c387df4c9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Reporting Engineer</t>
+          <t>Sr. Engineer, Machine Learning Operations</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>First Stop Health</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, Dataflow, CI/CD, Snowflake, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a5f900dec72ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=b2d9559a73ee7807</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Sr. Engineer, Machine Learning Operations</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Git, Kafka, MySQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=922ea8490463b8a7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Computer &amp; Electrical Engineer Software</t>
+          <t>Sr. Engineer, Machine Learning Operations</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Naval Nuclear Laboratory</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Mifflin, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21468c4f252a00d6</t>
+          <t>https://www.indeed.com/viewjob?jk=52d09ac6ccfd4493</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Computer &amp; Electrical Engineer Software</t>
+          <t>Sr. Engineer, Machine Learning Operations</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Naval Nuclear Laboratory</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Niskayuna, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e0f24a2c0edf7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7eef143523d46a81</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Computer &amp; Electrical Engineer Software</t>
+          <t>Machine Learning Engineer IV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Naval Nuclear Laboratory</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,52 +836,1487 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e4f5797489114e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e63a0ebf77000a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Connectivity Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Tableau, Power BI, Quicksight, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79952e54fe733362</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Database Reliability Engineer (Oracle &amp; Automation Focus)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, EC2, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=104eb630cab2bc86</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Jenkins, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc7b59779edbeba6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Charlotte, NC, US USA</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Databricks, PySpark, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Optimization Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Qcells</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Jenkins, Git, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a448122a2fa322</t>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82335d6b3b04cdec</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Optimization Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Qcells</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4136937203186974</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Optimization Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Qcells</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da59e787154dc22e</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analytics Intern</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Benjamin Moore</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Montvale, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, Azure ML, Snowflake, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2293b16fc0b0d29d</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Machine Learning &amp; Data Science - Summer 2026 Internships</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AI Engineer, TensorFlow, PyTorch, MLflow, Databricks, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96db92cab2cceb31</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-04.xlsx
+++ b/daily_matches/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>AI / Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>JobSPOT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,147 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=e124e38991469030</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Senior Web Architect, Full Stack</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Snowflake, Databricks, PostgreSQL, NoSQL, Power BI, Python, SQL</t>
+          <t>Generative AI, RAG, CI/CD, Git, PostgreSQL, MySQL, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556f55def0d3f2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Data Science Analyst I - Enterprise Data &amp; Analytics - Digital and Technology Partners - Hybrid/Onsite</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mount Sinai Health System</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Git, Databricks, PySpark, Tableau, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d19f2c58d3a5238</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AI Scientist 2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Keras, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e801ff1a5022b474</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AI Scientist 2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Keras, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e851fd7aef35214</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c76c468a954e5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-04.xlsx
+++ b/daily_matches/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=176afb0ac80a4191</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI / Machine Learning Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JobSPOT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>Generative AI, AWS SageMaker, EC2, Redshift, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,287 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e124e38991469030</t>
+          <t>https://www.indeed.com/viewjob?jk=be47bff9f1c0f69d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Web Architect, Full Stack</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, S3, EC2, Glue, Athena, Terraform, Python, R</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df69083a5f5407d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SQL Server Database Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IDBNY</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, Snowflake, Databricks, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>senior data scientist - Pricing (Seattle, WA)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Starbucks</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>12.2</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Git, PostgreSQL, MySQL, MongoDB, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Databricks, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c76c468a954e5</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7658bff5bfb1c481</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data Scientist- AI Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Redwood Software Inc.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Copilot, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcaeabb40cc4141c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Risk Data Scientist</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CashMax</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, FastAPI, CI/CD, Power BI, Python, SQL, R, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ecea50201088d71</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Applied Data &amp; Analytics Bachelor's Intern</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kaiser Permanente</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tustin, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d546c96bc79d458</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Medius Software Inc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28ad6369b1da4f88</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>First Quality</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12645497027ef48d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-04.xlsx
+++ b/daily_matches/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176afb0ac80a4191</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>AIML Engineer III – Treasury and Lending Platforms</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, AWS SageMaker, EC2, Redshift, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Redshift</t>
+          <t>LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, AKS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be47bff9f1c0f69d</t>
+          <t>https://www.indeed.com/viewjob?jk=0320d7ad28bcb315</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Recursion Technologies, Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, S3, EC2, Glue, Athena, Terraform, Python, R</t>
+          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df69083a5f5407d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6138105d361c110c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SQL Server Database Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IDBNY</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Snowflake, Databricks, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Cortex, Snowflake, Databricks, PySpark, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>senior data scientist - Pricing (Seattle, WA)</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Databricks, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7658bff5bfb1c481</t>
+          <t>https://www.indeed.com/viewjob?jk=6304fa25b90dcc51</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist- AI Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Redwood Software Inc.</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Copilot, Python, SQL, R, Scala</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcaeabb40cc4141c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4e15b6a0305b12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Risk Data Scientist</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CashMax</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FastAPI, CI/CD, Power BI, Python, SQL, R, Hypothesis Testing, A/B Testing</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecea50201088d71</t>
+          <t>https://www.indeed.com/viewjob?jk=40b321afc8939ff9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Applied Data &amp; Analytics Bachelor's Intern</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Proxet</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d546c96bc79d458</t>
+          <t>https://www.indeed.com/viewjob?jk=2c123eaea5e60741</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Medius Software Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,182 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ad6369b1da4f88</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd17d60185ddd02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d945b5b13d75a94</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior II DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Akamai</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12645497027ef48d</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d539fefb30d13c58</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Global AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PCI Pharma Services</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rockford, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Hadoop, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fd3cfd1022f1a0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VIE - Digital Engineer F/H</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Framatome</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lynchburg, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, S3, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad8fe3c5c0efb1b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Platform Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Avant</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90792ae31b472e2f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-04.xlsx
+++ b/daily_matches/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Git</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIML Engineer III – Treasury and Lending Platforms</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, AKS</t>
+          <t>Data Scientist, RAG, Prompt Engineering, BigQuery, Dataflow, Docker, Kubernetes, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0320d7ad28bcb315</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior MLOps Engineer – LLMOps</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recursion Technologies, Inc</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6138105d361c110c</t>
+          <t>https://www.indeed.com/viewjob?jk=d64b1b7a7032d981</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Cortex, Snowflake, Databricks, PySpark, Tableau, Power BI</t>
+          <t>Data Scientist, RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Snowflake, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Software Engineer - Backend/Cloud Services</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, S3, Docker, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6304fa25b90dcc51</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5afc3cedfad680</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4e15b6a0305b12</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, Docker, Kubernetes, Terraform, BigQuery, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b321afc8939ff9</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Proxet</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, BigQuery, MLflow, Kubernetes, CI/CD, Terraform, Snowflake, BigQuery, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c123eaea5e60741</t>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, BigQuery, MLflow, Kubernetes, CI/CD, Terraform, Snowflake, BigQuery, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd17d60185ddd02</t>
+          <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, Docker, Kubernetes, Terraform, BigQuery, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d945b5b13d75a94</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior II DevOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Akamai</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d539fefb30d13c58</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Global AI Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PCI Pharma Services</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rockford, IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Hadoop, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fd3cfd1022f1a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b85388834a4084ab</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VIE - Digital Engineer F/H</t>
+          <t>Site Reliability Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Framatome</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lynchburg, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, S3, Git, Python, SQL, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,427 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8fe3c5c0efb1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5c06bb3f40b47ce1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>Artificial Intelligence (AI) Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Avant</t>
+          <t>Wet Coast Logistics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Melbourne, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bd8192343ef9694</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Market Research Consultant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Chicago, IL, US USA</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9aba58451f90361</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, AKS, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e22b5174ebc40fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer - Master</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, BigQuery, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>REFRAME Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>North Carolina State University</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13bc35caa340fe00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Concord, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73c9ddaa57f09129</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Founding Reliability &amp; Performance Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90792ae31b472e2f</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Kubernetes, AKS, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4e239e707f10730</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Terraform, BigQuery, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0ef470a847776fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Graph Analytics</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Hadoop, Dask, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f92167868bb5bf77</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Graph Analytics</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Hadoop, Dask, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d34c1d9aa17bb171</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Business Intelligence Architect (AWS)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Menasha Corporation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Neenah, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Data Lake, Terraform, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbb47d5a465d37be</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Business Data Scientist, YouTube Partner Program</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Youtube</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>San Bruno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34594ee380915358</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-04.xlsx
+++ b/daily_matches/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
+          <t>Data Scientist, RAG, Redshift, Synapse, Snowflake, Databricks, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, BigQuery, Dataflow, Docker, Kubernetes, Terraform, Git, BigQuery</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer – LLMOps</t>
+          <t>Google Cloud Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Cloudious</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, CI/CD, BigQuery, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d64b1b7a7032d981</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc517b82db140b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>Software Engineer III - Machine Learning &amp; Operations</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Snowflake, BigQuery, Kafka, Python</t>
+          <t>Generative AI, RAG, S3, CI/CD, Terraform, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=f93fdf3ab70c897e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend/Cloud Services</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, S3, Docker, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, Cortex, Snowflake, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5afc3cedfad680</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Enterprise Data Platform Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+          <t>RAG, S3, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Software Engineer - Profiles, Identity, Consent</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Docker, Kubernetes, Terraform, BigQuery, Kafka, Python, SQL</t>
+          <t>Docker, Kubernetes, Terraform, Git, Kafka, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=227c3b976a1255e9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, MLflow, Kubernetes, CI/CD, Terraform, Snowflake, BigQuery, Python</t>
+          <t>RAG, S3, CI/CD, Terraform, Snowflake, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, MLflow, Kubernetes, CI/CD, Terraform, Snowflake, BigQuery, Python</t>
+          <t>Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
+          <t>https://www.indeed.com/viewjob?jk=66bca8b2e3f0b71a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>Intern – Computer Science - Advance Packaging Technology Development (APTD)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Docker, Kubernetes, Terraform, BigQuery, Kafka, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Keras, NoSQL, Matplotlib, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=043414c7d7b04e47</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer II / Senior Engineer, Life Sciences Data Science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Machine Learning Engineer, RAG, S3, EC2, Kubernetes, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=1086117745cef393</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Git, Hadoop, MongoDB, NoSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85388834a4084ab</t>
+          <t>https://www.indeed.com/viewjob?jk=39455378c5e18ef2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - Intermediate</t>
+          <t>Machine Learning Scientist, Personalization (Open to Remote)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c06bb3f40b47ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=314feec98ea7345a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Engineer III</t>
+          <t>Senior Machine Learning - Avatar, Core AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wet Coast Logistics</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Melbourne, FL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bd8192343ef9694</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b4f0d4501495</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Market Research Consultant</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Numonix</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9aba58451f90361</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbb9dd536ad1827</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, AKS, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+          <t>RAG, BigQuery, Dataflow, Git, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e22b5174ebc40fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Software Engineer III - React, JavaScript, TypeScript</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, BigQuery, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=9a893a6064972997</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>REFRAME Full Stack Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Hadoop, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bc35caa340fe00</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8e0185bbc9ba7d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Software Engineer (GenAI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Clario</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Optimization</t>
+          <t>Generative AI, PyTorch, FastAPI, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c9ddaa57f09129</t>
+          <t>https://www.indeed.com/viewjob?jk=b2009a44471c6117</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Founding Reliability &amp; Performance Engineer</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fubo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kubernetes, AKS, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Kafka, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e239e707f10730</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fde00cda859eda</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Associate Software Engineer - Java</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Terraform, BigQuery, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, PostgreSQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ef470a847776fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b750b12b29bd526c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Graph Analytics</t>
+          <t>Associate Software Engineer - Java</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Hadoop, Dask, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, PostgreSQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92167868bb5bf77</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7e3812454254a8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Graph Analytics</t>
+          <t>Associate Software Engineer - Java</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Danbury, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Hadoop, Dask, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, PostgreSQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34c1d9aa17bb171</t>
+          <t>https://www.indeed.com/viewjob?jk=f271fffc470bbf10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect (AWS)</t>
+          <t>Associate Software Engineer - Java</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Menasha Corporation</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Neenah, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Data Lake, Terraform, SQL, R, Scala, Optimization</t>
+          <t>RAG, CI/CD, Jenkins, Git, PostgreSQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,42 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb47d5a465d37be</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Business Data Scientist, YouTube Partner Program</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Youtube</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>San Bruno, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34594ee380915358</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e77c8aaf4b7bda</t>
         </is>
       </c>
     </row>
